--- a/20250820_drying_rate_of_LBW2_soil.xlsx
+++ b/20250820_drying_rate_of_LBW2_soil.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ik/codes/cascade/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B36449D2-8CD0-1E46-9CC0-4DAE100ED704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99406966-47D9-F74D-8DCC-A16AF00F059E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="660" windowWidth="25440" windowHeight="15320" xr2:uid="{5B16C7C3-6B16-1C4C-A879-A01D89B7CAEF}"/>
   </bookViews>
   <sheets>
     <sheet name="20250820_drying_rate_of_LBW2_so" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BA4A25-A136-9242-9F34-AA5A181C4643}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -582,206 +582,295 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>45890.417361111111</v>
+      </c>
+      <c r="B11">
+        <v>68</v>
+      </c>
+      <c r="C11">
+        <v>69.77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B18" t="s">
         <v>5</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C18" t="s">
         <v>6</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D18" t="s">
         <v>4</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
         <f>A4-A$4</f>
         <v>0</v>
       </c>
-      <c r="B14">
+      <c r="B19">
         <f>B4-$F$3</f>
         <v>75</v>
       </c>
-      <c r="C14">
+      <c r="C19">
         <f>C4-$F$3</f>
         <v>75.09</v>
       </c>
-      <c r="D14">
-        <f>A14</f>
+      <c r="D19">
+        <f>A19</f>
         <v>0</v>
       </c>
-      <c r="E14">
+      <c r="E19">
         <f>(B4-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>75.621546961325961</v>
       </c>
-      <c r="F14">
+      <c r="F19">
         <f>(C4-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>75.84654696132597</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
         <f>A5-A$4</f>
         <v>0.96666666666715173</v>
       </c>
-      <c r="B15">
+      <c r="B20">
         <f>B5-$F$3</f>
         <v>73.61</v>
       </c>
-      <c r="C15">
+      <c r="C20">
         <f>C5-$F$3</f>
         <v>73.78</v>
       </c>
-      <c r="D15">
-        <f t="shared" ref="D15:D20" si="0">A15</f>
+      <c r="D20">
+        <f t="shared" ref="D20:D25" si="0">A20</f>
         <v>0.96666666666715173</v>
       </c>
-      <c r="E15">
-        <f t="shared" ref="E15:F15" si="1">(B5-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+      <c r="E20">
+        <f>(B5-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>72.146546961325953</v>
       </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
+      <c r="F20">
+        <f>(C5-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>72.571546961325964</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
         <f>A6-A$4</f>
         <v>1.9652777777810115</v>
       </c>
-      <c r="B16">
+      <c r="B21">
         <f>B6-$F$3</f>
         <v>72.23</v>
       </c>
-      <c r="C16">
+      <c r="C21">
         <f>C6-$F$3</f>
         <v>72.540000000000006</v>
       </c>
-      <c r="D16">
+      <c r="D21">
         <f t="shared" si="0"/>
         <v>1.9652777777810115</v>
       </c>
-      <c r="E16">
-        <f t="shared" ref="E16:F16" si="2">(B6-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+      <c r="E21">
+        <f>(B6-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>68.696546961325964</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="2"/>
+      <c r="F21">
+        <f>(C6-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>69.47154696132597</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
         <f>A7-A$4</f>
         <v>3.882638888891961</v>
       </c>
-      <c r="B17">
+      <c r="B22">
         <f>B7-$F$3</f>
         <v>69.27000000000001</v>
       </c>
-      <c r="C17">
+      <c r="C22">
         <f>C7-$F$3</f>
         <v>69.97</v>
       </c>
-      <c r="D17">
+      <c r="D22">
         <f t="shared" si="0"/>
         <v>3.882638888891961</v>
       </c>
-      <c r="E17">
-        <f t="shared" ref="E17:F17" si="3">(B7-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+      <c r="E22">
+        <f>(B7-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>61.29654696132598</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="3"/>
+      <c r="F22">
+        <f>(C7-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>63.046546961325959</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
         <f>A8-A$4</f>
         <v>5.8409722222277196</v>
       </c>
-      <c r="B18">
+      <c r="B23">
         <f>B8-$F$3</f>
         <v>67.06</v>
       </c>
-      <c r="C18">
+      <c r="C23">
         <f>C8-$F$3</f>
         <v>68.06</v>
       </c>
-      <c r="D18">
+      <c r="D23">
         <f t="shared" si="0"/>
         <v>5.8409722222277196</v>
       </c>
-      <c r="E18">
-        <f t="shared" ref="E18:F18" si="4">(B8-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+      <c r="E23">
+        <f>(B8-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>55.771546961325967</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="4"/>
+      <c r="F23">
+        <f>(C8-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>58.271546961325967</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
         <f>A9-A$4</f>
         <v>6.8125</v>
       </c>
-      <c r="B19">
+      <c r="B24">
         <f>B9-$F$3</f>
         <v>65.59</v>
       </c>
-      <c r="C19">
+      <c r="C24">
         <f>C9-$F$3</f>
         <v>66.84</v>
       </c>
-      <c r="D19">
+      <c r="D24">
         <f t="shared" si="0"/>
         <v>6.8125</v>
       </c>
-      <c r="E19">
-        <f t="shared" ref="E19:F19" si="5">(B9-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+      <c r="E24">
+        <f>(B9-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>52.09654696132597</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="5"/>
+      <c r="F24">
+        <f>(C9-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>55.22154696132597</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25">
         <f>A10-A$4</f>
         <v>8.8145833333328483</v>
       </c>
-      <c r="B20">
+      <c r="B25">
         <f>B10-$F$3</f>
         <v>63</v>
       </c>
-      <c r="C20">
+      <c r="C25">
         <f>C10-$F$3</f>
         <v>64.61</v>
       </c>
-      <c r="D20">
+      <c r="D25">
         <f t="shared" si="0"/>
         <v>8.8145833333328483</v>
       </c>
-      <c r="E20">
-        <f t="shared" ref="E20:F20" si="6">(B10-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+      <c r="E25">
+        <f>(B10-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>45.621546961325961</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="6"/>
+      <c r="F25">
+        <f>(C10-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
         <v>49.64654696132596</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <f>A11-A$4</f>
+        <v>9.8041666666686069</v>
+      </c>
+      <c r="B26">
+        <f>B11-$F$3</f>
+        <v>61.480000000000004</v>
+      </c>
+      <c r="C26">
+        <f>C11-$F$3</f>
+        <v>63.25</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ref="D26:D28" si="1">A26</f>
+        <v>9.8041666666686069</v>
+      </c>
+      <c r="E26">
+        <f>(B11-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>41.821546961325971</v>
+      </c>
+      <c r="F26">
+        <f>(C11-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>46.246546961325961</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f>A12-A$4</f>
+        <v>-45880.613194444442</v>
+      </c>
+      <c r="B27">
+        <f>B12-$F$3</f>
+        <v>-6.52</v>
+      </c>
+      <c r="C27">
+        <f>C12-$F$3</f>
+        <v>-6.52</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>-45880.613194444442</v>
+      </c>
+      <c r="E27">
+        <f>(B12-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>-128.17845303867401</v>
+      </c>
+      <c r="F27">
+        <f>(C12-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>-128.17845303867401</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="e">
+        <f>A18-A$4</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B28" t="e">
+        <f t="shared" ref="B28:C28" si="2">B18-$F$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C28" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D28" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E28" t="e">
+        <f>(B18-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F28" t="e">
+        <f>(C18-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/20250820_drying_rate_of_LBW2_soil.xlsx
+++ b/20250820_drying_rate_of_LBW2_soil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ik/codes/cascade/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99406966-47D9-F74D-8DCC-A16AF00F059E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56034A2C-DAB9-5B45-833D-5F4D6CBA8A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="660" windowWidth="25440" windowHeight="15320" xr2:uid="{5B16C7C3-6B16-1C4C-A879-A01D89B7CAEF}"/>
   </bookViews>
@@ -77,7 +77,7 @@
     <t>Initial soil and water mass (g)</t>
   </si>
   <si>
-    <t>Pink = Soil 1, White = Soil 2</t>
+    <t>Pink = Dish 1, White = Dish 2</t>
   </si>
 </sst>
 </file>
@@ -113,10 +113,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BA4A25-A136-9242-9F34-AA5A181C4643}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -499,8 +500,7 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <f>0.8</f>
-        <v>0.8</v>
+        <v>0.67500000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -517,8 +517,7 @@
         <v>8</v>
       </c>
       <c r="F5">
-        <f>0.95/9.05</f>
-        <v>0.10497237569060772</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -593,6 +592,39 @@
         <v>69.77</v>
       </c>
     </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>45892.674305555556</v>
+      </c>
+      <c r="B12">
+        <v>65.150000000000006</v>
+      </c>
+      <c r="C12">
+        <v>67.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>45894.550694444442</v>
+      </c>
+      <c r="B13">
+        <v>62.31</v>
+      </c>
+      <c r="C13">
+        <v>64.680000000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>45895.460416666669</v>
+      </c>
+      <c r="B14">
+        <v>60.9</v>
+      </c>
+      <c r="C14">
+        <v>63.4</v>
+      </c>
+    </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>4</v>
@@ -615,15 +647,15 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f>A4-A$4</f>
+        <f t="shared" ref="A19:A32" si="0">A4-A$4</f>
         <v>0</v>
       </c>
       <c r="B19">
-        <f>B4-$F$3</f>
+        <f t="shared" ref="B19:C27" si="1">B4-$F$3</f>
         <v>75</v>
       </c>
       <c r="C19">
-        <f>C4-$F$3</f>
+        <f t="shared" si="1"/>
         <v>75.09</v>
       </c>
       <c r="D19">
@@ -631,246 +663,350 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <f>(B4-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>75.621546961325961</v>
+        <f t="shared" ref="E19:E27" si="2">(B4-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>88.888888888888886</v>
       </c>
       <c r="F19">
-        <f>(C4-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>75.84654696132597</v>
+        <f t="shared" ref="F19:F27" si="3">(C4-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>89.155555555555566</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f>A5-A$4</f>
+        <f t="shared" si="0"/>
         <v>0.96666666666715173</v>
       </c>
       <c r="B20">
-        <f>B5-$F$3</f>
+        <f t="shared" si="1"/>
         <v>73.61</v>
       </c>
       <c r="C20">
-        <f>C5-$F$3</f>
+        <f t="shared" si="1"/>
         <v>73.78</v>
       </c>
       <c r="D20">
-        <f t="shared" ref="D20:D25" si="0">A20</f>
+        <f t="shared" ref="D20:D25" si="4">A20</f>
         <v>0.96666666666715173</v>
       </c>
       <c r="E20">
-        <f>(B5-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>72.146546961325953</v>
+        <f t="shared" si="2"/>
+        <v>84.770370370370358</v>
       </c>
       <c r="F20">
-        <f>(C5-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>72.571546961325964</v>
+        <f t="shared" si="3"/>
+        <v>85.274074074074065</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f>A6-A$4</f>
+        <f t="shared" si="0"/>
         <v>1.9652777777810115</v>
       </c>
       <c r="B21">
-        <f>B6-$F$3</f>
+        <f t="shared" si="1"/>
         <v>72.23</v>
       </c>
       <c r="C21">
-        <f>C6-$F$3</f>
+        <f t="shared" si="1"/>
         <v>72.540000000000006</v>
       </c>
       <c r="D21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>1.9652777777810115</v>
       </c>
       <c r="E21">
-        <f>(B6-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>68.696546961325964</v>
+        <f t="shared" si="2"/>
+        <v>80.681481481481484</v>
       </c>
       <c r="F21">
-        <f>(C6-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>69.47154696132597</v>
+        <f t="shared" si="3"/>
+        <v>81.600000000000009</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f>A7-A$4</f>
+        <f t="shared" si="0"/>
         <v>3.882638888891961</v>
       </c>
       <c r="B22">
-        <f>B7-$F$3</f>
+        <f t="shared" si="1"/>
         <v>69.27000000000001</v>
       </c>
       <c r="C22">
-        <f>C7-$F$3</f>
+        <f t="shared" si="1"/>
         <v>69.97</v>
       </c>
       <c r="D22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>3.882638888891961</v>
       </c>
       <c r="E22">
-        <f>(B7-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>61.29654696132598</v>
+        <f t="shared" si="2"/>
+        <v>71.91111111111114</v>
       </c>
       <c r="F22">
-        <f>(C7-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>63.046546961325959</v>
+        <f t="shared" si="3"/>
+        <v>73.985185185185173</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f>A8-A$4</f>
+        <f t="shared" si="0"/>
         <v>5.8409722222277196</v>
       </c>
       <c r="B23">
-        <f>B8-$F$3</f>
+        <f t="shared" si="1"/>
         <v>67.06</v>
       </c>
       <c r="C23">
-        <f>C8-$F$3</f>
+        <f t="shared" si="1"/>
         <v>68.06</v>
       </c>
       <c r="D23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>5.8409722222277196</v>
       </c>
       <c r="E23">
-        <f>(B8-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>55.771546961325967</v>
+        <f t="shared" si="2"/>
+        <v>65.362962962962968</v>
       </c>
       <c r="F23">
-        <f>(C8-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>58.271546961325967</v>
+        <f t="shared" si="3"/>
+        <v>68.32592592592593</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f>A9-A$4</f>
+        <f t="shared" si="0"/>
         <v>6.8125</v>
       </c>
       <c r="B24">
-        <f>B9-$F$3</f>
+        <f t="shared" si="1"/>
         <v>65.59</v>
       </c>
       <c r="C24">
-        <f>C9-$F$3</f>
+        <f t="shared" si="1"/>
         <v>66.84</v>
       </c>
       <c r="D24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>6.8125</v>
       </c>
       <c r="E24">
-        <f>(B9-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>52.09654696132597</v>
+        <f t="shared" si="2"/>
+        <v>61.007407407407413</v>
       </c>
       <c r="F24">
-        <f>(C9-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>55.22154696132597</v>
+        <f t="shared" si="3"/>
+        <v>64.711111111111123</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f>A10-A$4</f>
+        <f t="shared" si="0"/>
         <v>8.8145833333328483</v>
       </c>
       <c r="B25">
-        <f>B10-$F$3</f>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="C25">
-        <f>C10-$F$3</f>
+        <f t="shared" si="1"/>
         <v>64.61</v>
       </c>
       <c r="D25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>8.8145833333328483</v>
       </c>
       <c r="E25">
-        <f>(B10-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>45.621546961325961</v>
+        <f t="shared" si="2"/>
+        <v>53.333333333333336</v>
       </c>
       <c r="F25">
-        <f>(C10-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>49.64654696132596</v>
+        <f t="shared" si="3"/>
+        <v>58.103703703703701</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f>A11-A$4</f>
+        <f t="shared" si="0"/>
         <v>9.8041666666686069</v>
       </c>
       <c r="B26">
-        <f>B11-$F$3</f>
+        <f t="shared" si="1"/>
         <v>61.480000000000004</v>
       </c>
       <c r="C26">
-        <f>C11-$F$3</f>
+        <f t="shared" si="1"/>
         <v>63.25</v>
       </c>
       <c r="D26">
-        <f t="shared" ref="D26:D28" si="1">A26</f>
+        <f t="shared" ref="D26:D27" si="5">A26</f>
         <v>9.8041666666686069</v>
       </c>
       <c r="E26">
-        <f>(B11-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>41.821546961325971</v>
+        <f t="shared" si="2"/>
+        <v>48.829629629629636</v>
       </c>
       <c r="F26">
-        <f>(C11-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>46.246546961325961</v>
+        <f t="shared" si="3"/>
+        <v>54.074074074074076</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f>A12-A$4</f>
+        <f t="shared" si="0"/>
+        <v>12.06111111111386</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="1"/>
+        <v>58.63000000000001</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="1"/>
+        <v>60.81</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="5"/>
+        <v>12.06111111111386</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="2"/>
+        <v>40.385185185185215</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="3"/>
+        <v>46.844444444444449</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>13.9375</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ref="B28:C28" si="6">B13-$F$3</f>
+        <v>55.790000000000006</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="6"/>
+        <v>58.160000000000011</v>
+      </c>
+      <c r="D28">
+        <f t="shared" ref="D28:D31" si="7">A28</f>
+        <v>13.9375</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ref="E28:E31" si="8">(B13-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>31.970370370370389</v>
+      </c>
+      <c r="F28">
+        <f t="shared" ref="F28:F31" si="9">(C13-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>38.992592592592622</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>14.847222222226264</v>
+      </c>
+      <c r="B29">
+        <f t="shared" ref="B29:C29" si="10">B14-$F$3</f>
+        <v>54.379999999999995</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="10"/>
+        <v>56.879999999999995</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="7"/>
+        <v>14.847222222226264</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="8"/>
+        <v>27.792592592592573</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="9"/>
+        <v>35.199999999999982</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <f t="shared" si="0"/>
         <v>-45880.613194444442</v>
       </c>
-      <c r="B27">
-        <f>B12-$F$3</f>
+      <c r="B30">
+        <f t="shared" ref="B30:C30" si="11">B15-$F$3</f>
         <v>-6.52</v>
       </c>
-      <c r="C27">
-        <f>C12-$F$3</f>
+      <c r="C30">
+        <f t="shared" si="11"/>
         <v>-6.52</v>
       </c>
-      <c r="D27">
-        <f t="shared" si="1"/>
+      <c r="D30">
+        <f t="shared" si="7"/>
         <v>-45880.613194444442</v>
       </c>
-      <c r="E27">
-        <f>(B12-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>-128.17845303867401</v>
-      </c>
-      <c r="F27">
-        <f>(C12-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>-128.17845303867401</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="e">
-        <f>A18-A$4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B28" t="e">
-        <f t="shared" ref="B28:C28" si="2">B18-$F$3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C28" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D28" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E28" t="e">
-        <f>(B18-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F28" t="e">
-        <f>(C18-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
-        <v>#VALUE!</v>
+      <c r="E30">
+        <f t="shared" si="8"/>
+        <v>-152.65185185185183</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="9"/>
+        <v>-152.65185185185183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>-45880.613194444442</v>
+      </c>
+      <c r="B31">
+        <f t="shared" ref="B31:C31" si="12">B16-$F$3</f>
+        <v>-6.52</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="12"/>
+        <v>-6.52</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="7"/>
+        <v>-45880.613194444442</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="8"/>
+        <v>-152.65185185185183</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="9"/>
+        <v>-152.65185185185183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>-45880.613194444442</v>
+      </c>
+      <c r="B32">
+        <f t="shared" ref="B32:C32" si="13">B17-$F$3</f>
+        <v>-6.52</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="13"/>
+        <v>-6.52</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32" si="14">A32</f>
+        <v>-45880.613194444442</v>
+      </c>
+      <c r="E32">
+        <f t="shared" ref="E32" si="15">(B17-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>-152.65185185185183</v>
+      </c>
+      <c r="F32">
+        <f t="shared" ref="F32" si="16">(C17-$F$3-$F$6+$F$5*$F$6)/$F$4/$F$6*100</f>
+        <v>-152.65185185185183</v>
       </c>
     </row>
   </sheetData>
